--- a/final_lists/rc_assets_final_scanned_list/output_excel/rc_assets_final_scanned_bid_list_CORRECTED.xlsx
+++ b/final_lists/rc_assets_final_scanned_list/output_excel/rc_assets_final_scanned_bid_list_CORRECTED.xlsx
@@ -33,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,9 +43,13 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +93,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
@@ -119,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -142,7 +151,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -151,10 +160,13 @@
     <xf numFmtId="164" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -163,10 +175,22 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -542,49 +566,49 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
     <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="38" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
     <col width="23" customWidth="1" min="24" max="24"/>
     <col width="23" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
-    <col width="37" customWidth="1" min="28" max="28"/>
-    <col width="38" customWidth="1" min="29" max="29"/>
-    <col width="30" customWidth="1" min="30" max="30"/>
-    <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="38" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="34" customWidth="1" min="30" max="30"/>
+    <col width="48" customWidth="1" min="31" max="31"/>
+    <col width="48" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="16" customWidth="1" min="34" max="34"/>
     <col width="19" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
-    <col width="45" customWidth="1" min="37" max="37"/>
-    <col width="38" customWidth="1" min="38" max="38"/>
-    <col width="38" customWidth="1" min="39" max="39"/>
+    <col width="48" customWidth="1" min="37" max="37"/>
+    <col width="48" customWidth="1" min="38" max="38"/>
+    <col width="48" customWidth="1" min="39" max="39"/>
     <col width="15" customWidth="1" min="40" max="40"/>
     <col hidden="1" width="18" customWidth="1" min="41" max="41"/>
     <col hidden="1" width="24" customWidth="1" min="42" max="42"/>
     <col hidden="1" width="24" customWidth="1" min="43" max="43"/>
-    <col hidden="1" width="32" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="26" customWidth="1" min="44" max="44"/>
     <col hidden="1" width="17" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -811,7 +835,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="7" t="n">
         <v>2</v>
       </c>
@@ -1000,7 +1024,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="7" t="n">
         <v>10</v>
       </c>
@@ -1189,7 +1213,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>32</v>
       </c>
@@ -1378,7 +1402,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="12" t="n">
         <v>41</v>
       </c>
@@ -1395,13 +1419,13 @@
       <c r="D5" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="13" t="n">
         <v>148</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="13" t="n">
         <v>148</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -1414,13 +1438,13 @@
           <t>3128 N TROOST PL E</t>
         </is>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="14" t="n">
         <v>3389.11</v>
       </c>
       <c r="K5" s="10" t="n">
         <v>17000</v>
       </c>
-      <c r="L5" s="13" t="n">
+      <c r="L5" s="14" t="n">
         <v>13610.89</v>
       </c>
       <c r="M5" s="12" t="inlineStr">
@@ -1567,153 +1591,153 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>$1,500–$2,000</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>41</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="16" t="n">
         <v>204</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="16" t="n">
         <v>204</v>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>13850-93-05-10570</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>2621 E ADMIRAL CT N</t>
         </is>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="17" t="n">
         <v>1759.82</v>
       </c>
       <c r="K6" s="10" t="n">
         <v>8000</v>
       </c>
-      <c r="L6" s="15" t="n">
+      <c r="L6" s="17" t="n">
         <v>6240.18</v>
       </c>
-      <c r="M6" s="14" t="inlineStr">
+      <c r="M6" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="N6" s="14" t="inlineStr">
+      <c r="N6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Checked </t>
         </is>
       </c>
-      <c r="O6" s="14" t="inlineStr">
-        <is>
-          <t>Not Checked</t>
-        </is>
-      </c>
-      <c r="P6" s="14" t="inlineStr">
-        <is>
-          <t>Not Checked</t>
-        </is>
-      </c>
-      <c r="Q6" s="14" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="P6" s="15" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="R6" s="14" t="inlineStr"/>
-      <c r="S6" s="14" t="inlineStr">
+      <c r="R6" s="15" t="inlineStr"/>
+      <c r="S6" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="T6" s="14" t="inlineStr">
+      <c r="T6" s="15" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="U6" s="14" t="inlineStr">
+      <c r="U6" s="15" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="V6" s="14" t="inlineStr">
+      <c r="V6" s="15" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="W6" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="X6" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Y6" s="14" t="inlineStr">
+      <c r="W6" s="15" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="X6" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Y6" s="15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="Z6" s="14" t="inlineStr">
+      <c r="Z6" s="15" t="inlineStr">
         <is>
           <t>Possible Match</t>
         </is>
       </c>
-      <c r="AA6" s="14" t="inlineStr">
+      <c r="AA6" s="15" t="inlineStr">
         <is>
           <t>Admiral corridor</t>
         </is>
       </c>
-      <c r="AB6" s="14" t="inlineStr">
+      <c r="AB6" s="15" t="inlineStr">
         <is>
           <t>corridor-level reinvestment context</t>
         </is>
       </c>
-      <c r="AC6" s="14" t="inlineStr">
+      <c r="AC6" s="15" t="inlineStr">
         <is>
           <t>City of Tulsa planning and corridor resources</t>
         </is>
       </c>
-      <c r="AD6" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="AE6" s="14" t="inlineStr">
+      <c r="AD6" s="15" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="AE6" s="15" t="inlineStr">
         <is>
           <t>Address appears on or near the Admiral corridor, where corridor-scale planning and reinvestment signals may matter.</t>
         </is>
       </c>
-      <c r="AF6" s="14" t="inlineStr">
+      <c r="AF6" s="15" t="inlineStr">
         <is>
           <t>Street/corridor name overlap supports only a possible corridor match, not a district-level certainty.</t>
         </is>
       </c>
-      <c r="AG6" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AH6" s="14" t="n">
+      <c r="AG6" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH6" s="15" t="n">
         <v>66</v>
       </c>
       <c r="AI6" s="11" t="inlineStr">
@@ -1721,50 +1745,50 @@
           <t>Watchlist</t>
         </is>
       </c>
-      <c r="AJ6" s="14" t="inlineStr">
+      <c r="AJ6" s="15" t="inlineStr">
         <is>
           <t>Priority 3</t>
         </is>
       </c>
-      <c r="AK6" s="14" t="inlineStr">
+      <c r="AK6" s="15" t="inlineStr">
         <is>
           <t>Parcel 13850-93-05-10570 at 2621 E ADMIRAL CT N has opening bid 1759.82, max bid 8000.0, grade C, color Blue, crime risk Medium, and economic signal Positive.</t>
         </is>
       </c>
-      <c r="AL6" s="14" t="inlineStr">
+      <c r="AL6" s="15" t="inlineStr">
         <is>
           <t>crime context Medium</t>
         </is>
       </c>
-      <c r="AM6" s="14" t="inlineStr">
+      <c r="AM6" s="15" t="inlineStr">
         <is>
           <t>Verify title, liens, occupancy, and auction-order assumptions before bidding.</t>
         </is>
       </c>
-      <c r="AN6" s="14" t="inlineStr">
+      <c r="AN6" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AO6" s="14" t="n">
+      <c r="AO6" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="AP6" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="14" t="inlineStr">
+      <c r="AP6" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="15" t="inlineStr">
         <is>
           <t>kept</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="7" t="n">
         <v>33</v>
       </c>
@@ -1953,7 +1977,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="12" t="n">
         <v>29</v>
       </c>
@@ -1970,13 +1994,13 @@
       <c r="D8" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="13" t="n">
         <v>337</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="13" t="n">
         <v>337</v>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -1989,13 +2013,13 @@
           <t>1864 N OWASSO AV E</t>
         </is>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="14" t="n">
         <v>3140.35</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="L8" s="13" t="n">
+      <c r="L8" s="14" t="n">
         <v>11859.65</v>
       </c>
       <c r="M8" s="12" t="inlineStr">
@@ -2142,7 +2166,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="7" t="n">
         <v>27</v>
       </c>
@@ -2331,7 +2355,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="7" t="n">
         <v>18</v>
       </c>
@@ -2520,7 +2544,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="n">
         <v>36</v>
       </c>
@@ -2709,7 +2733,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="7" t="n">
         <v>34</v>
       </c>
@@ -2898,7 +2922,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="7" t="n">
         <v>7</v>
       </c>
@@ -3087,7 +3111,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="12" t="n">
         <v>40</v>
       </c>
@@ -3104,13 +3128,13 @@
       <c r="D14" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="13" t="n">
         <v>512</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="13" t="n">
         <v>75</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="13" t="n">
         <v>512</v>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -3123,13 +3147,13 @@
           <t>419 E NEWTON PL N</t>
         </is>
       </c>
-      <c r="J14" s="13" t="n">
+      <c r="J14" s="14" t="n">
         <v>3388.99</v>
       </c>
       <c r="K14" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="L14" s="13" t="n">
+      <c r="L14" s="14" t="n">
         <v>11611.01</v>
       </c>
       <c r="M14" s="12" t="inlineStr">
@@ -3276,7 +3300,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
@@ -3465,7 +3489,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="7" t="n">
         <v>15</v>
       </c>
@@ -3654,7 +3678,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="7" t="n">
         <v>22</v>
       </c>
@@ -3843,7 +3867,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="7" t="n">
         <v>17</v>
       </c>
@@ -4032,7 +4056,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="7" t="n">
         <v>21</v>
       </c>
@@ -4221,7 +4245,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="42" customHeight="1">
       <c r="A20" s="7" t="n">
         <v>5</v>
       </c>
@@ -4410,7 +4434,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="42" customHeight="1">
       <c r="A21" s="7" t="n">
         <v>8</v>
       </c>
@@ -4599,7 +4623,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="7" t="n">
         <v>9</v>
       </c>
@@ -4788,7 +4812,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="42" customHeight="1">
       <c r="A23" s="7" t="n">
         <v>4</v>
       </c>
@@ -4977,7 +5001,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="42" customHeight="1">
       <c r="A24" s="7" t="n">
         <v>35</v>
       </c>
@@ -5166,7 +5190,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="42" customHeight="1">
       <c r="A25" s="7" t="n">
         <v>25</v>
       </c>
@@ -5355,7 +5379,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="42" customHeight="1">
       <c r="A26" s="7" t="n">
         <v>31</v>
       </c>
@@ -5544,7 +5568,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="42" customHeight="1">
       <c r="A27" s="7" t="n">
         <v>38</v>
       </c>
@@ -5733,7 +5757,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="42" customHeight="1">
       <c r="A28" s="7" t="n">
         <v>13</v>
       </c>
@@ -5922,7 +5946,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="42" customHeight="1">
       <c r="A29" s="7" t="n">
         <v>28</v>
       </c>
@@ -6111,7 +6135,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="42" customHeight="1">
       <c r="A30" s="12" t="n">
         <v>16</v>
       </c>
@@ -6128,13 +6152,13 @@
       <c r="D30" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="E30" s="13" t="n">
         <v>971</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="13" t="n">
         <v>144</v>
       </c>
-      <c r="G30" s="8" t="n">
+      <c r="G30" s="13" t="n">
         <v>971</v>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -6147,13 +6171,13 @@
           <t>6369 N BOULDER AV W</t>
         </is>
       </c>
-      <c r="J30" s="13" t="n">
+      <c r="J30" s="14" t="n">
         <v>1693.83</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="L30" s="13" t="n">
+      <c r="L30" s="14" t="n">
         <v>13306.17</v>
       </c>
       <c r="M30" s="12" t="inlineStr">
@@ -6300,7 +6324,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="42" customHeight="1">
       <c r="A31" s="12" t="n">
         <v>19</v>
       </c>
@@ -6317,13 +6341,13 @@
       <c r="D31" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="13" t="n">
         <v>1047</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="13" t="n">
         <v>153</v>
       </c>
-      <c r="G31" s="8" t="n">
+      <c r="G31" s="13" t="n">
         <v>963</v>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -6336,13 +6360,13 @@
           <t>3930 S 61 AV W</t>
         </is>
       </c>
-      <c r="J31" s="13" t="n">
+      <c r="J31" s="14" t="n">
         <v>1716.68</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>14000</v>
       </c>
-      <c r="L31" s="13" t="n">
+      <c r="L31" s="14" t="n">
         <v>12283.32</v>
       </c>
       <c r="M31" s="12" t="inlineStr">
@@ -6441,7 +6465,7 @@
       <c r="AH31" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="AI31" s="7" t="inlineStr">
+      <c r="AI31" s="18" t="inlineStr">
         <is>
           <t>Strong Candidate</t>
         </is>
@@ -6489,7 +6513,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="42" customHeight="1">
       <c r="A32" s="12" t="n">
         <v>11</v>
       </c>
@@ -6506,13 +6530,13 @@
       <c r="D32" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="E32" s="13" t="n">
         <v>1241</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F32" s="13" t="n">
         <v>182</v>
       </c>
-      <c r="G32" s="8" t="n">
+      <c r="G32" s="13" t="n">
         <v>1081</v>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -6525,13 +6549,13 @@
           <t>1118 E 50 PL N</t>
         </is>
       </c>
-      <c r="J32" s="13" t="n">
+      <c r="J32" s="14" t="n">
         <v>1317.38</v>
       </c>
       <c r="K32" s="10" t="n">
         <v>12000</v>
       </c>
-      <c r="L32" s="13" t="n">
+      <c r="L32" s="14" t="n">
         <v>10682.62</v>
       </c>
       <c r="M32" s="12" t="inlineStr">
@@ -6678,7 +6702,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="42" customHeight="1">
       <c r="A33" s="12" t="n">
         <v>37</v>
       </c>
@@ -6695,13 +6719,13 @@
       <c r="D33" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="13" t="n">
         <v>1249</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="13" t="n">
         <v>184</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="13" t="n">
         <v>1249</v>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -6714,13 +6738,13 @@
           <t>1641 E 56 ST N TULSA</t>
         </is>
       </c>
-      <c r="J33" s="13" t="n">
+      <c r="J33" s="14" t="n">
         <v>3314.33</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="L33" s="13" t="n">
+      <c r="L33" s="14" t="n">
         <v>11685.67</v>
       </c>
       <c r="M33" s="12" t="inlineStr">
@@ -6867,145 +6891,145 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="14" t="n">
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>$1,000–$1,500</t>
         </is>
       </c>
-      <c r="D34" s="14" t="n">
+      <c r="D34" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="E34" s="16" t="n">
         <v>1303</v>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F34" s="16" t="n">
         <v>193</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="16" t="n">
         <v>1303</v>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="15" t="inlineStr">
         <is>
           <t>96203-62-03-50220</t>
         </is>
       </c>
-      <c r="I34" s="14" t="inlineStr">
+      <c r="I34" s="15" t="inlineStr">
         <is>
           <t>18911 S 29 AV W</t>
         </is>
       </c>
-      <c r="J34" s="15" t="n">
+      <c r="J34" s="17" t="n">
         <v>1064.76</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>4000</v>
       </c>
-      <c r="L34" s="15" t="n">
+      <c r="L34" s="17" t="n">
         <v>2935.24</v>
       </c>
-      <c r="M34" s="14" t="inlineStr">
+      <c r="M34" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="N34" s="14" t="inlineStr">
-        <is>
-          <t>Not Checked</t>
-        </is>
-      </c>
-      <c r="O34" s="14" t="inlineStr">
-        <is>
-          <t>Not Checked</t>
-        </is>
-      </c>
-      <c r="P34" s="14" t="inlineStr">
-        <is>
-          <t>Not Checked</t>
-        </is>
-      </c>
-      <c r="Q34" s="14" t="inlineStr">
+      <c r="N34" s="15" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="O34" s="15" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="P34" s="15" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="Q34" s="15" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="R34" s="14" t="inlineStr"/>
-      <c r="S34" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="T34" s="14" t="inlineStr">
+      <c r="R34" s="15" t="inlineStr"/>
+      <c r="S34" s="15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="T34" s="15" t="inlineStr">
         <is>
           <t>South Tulsa / county-edge property, only broad area-level context available in this pass.</t>
         </is>
       </c>
-      <c r="U34" s="14" t="inlineStr">
+      <c r="U34" s="15" t="inlineStr">
         <is>
           <t>ZIP-Level</t>
         </is>
       </c>
-      <c r="V34" s="14" t="inlineStr">
+      <c r="V34" s="15" t="inlineStr">
         <is>
           <t>City of Tulsa public safety resources</t>
         </is>
       </c>
-      <c r="W34" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="X34" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Y34" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="Z34" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AA34" s="14" t="inlineStr"/>
-      <c r="AB34" s="14" t="inlineStr"/>
-      <c r="AC34" s="14" t="inlineStr">
+      <c r="W34" s="15" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="X34" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Y34" s="15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Z34" s="15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AA34" s="15" t="inlineStr"/>
+      <c r="AB34" s="15" t="inlineStr"/>
+      <c r="AC34" s="15" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="AD34" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="AE34" s="14" t="inlineStr">
+      <c r="AD34" s="15" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="AE34" s="15" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="AF34" s="14" t="inlineStr">
+      <c r="AF34" s="15" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="AG34" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AH34" s="14" t="n">
+      <c r="AG34" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH34" s="15" t="n">
         <v>65</v>
       </c>
       <c r="AI34" s="11" t="inlineStr">
@@ -7013,44 +7037,44 @@
           <t>Watchlist</t>
         </is>
       </c>
-      <c r="AJ34" s="14" t="inlineStr">
+      <c r="AJ34" s="15" t="inlineStr">
         <is>
           <t>Priority 3</t>
         </is>
       </c>
-      <c r="AK34" s="14" t="inlineStr">
+      <c r="AK34" s="15" t="inlineStr">
         <is>
           <t>Parcel 96203-62-03-50220 at 18911 S 29 AV W has opening bid 1064.76, max bid 4000.0, grade C, color Blue, crime risk Unknown, and economic signal Unknown.</t>
         </is>
       </c>
-      <c r="AL34" s="14" t="inlineStr">
+      <c r="AL34" s="15" t="inlineStr">
         <is>
           <t>crime context Unknown, economic signal Unknown</t>
         </is>
       </c>
-      <c r="AM34" s="14" t="inlineStr">
+      <c r="AM34" s="15" t="inlineStr">
         <is>
           <t>Verify title, liens, occupancy, and auction-order assumptions before bidding.</t>
         </is>
       </c>
-      <c r="AN34" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AO34" s="14" t="n">
+      <c r="AN34" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AO34" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="AP34" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS34" s="14" t="inlineStr">
+      <c r="AP34" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR34" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS34" s="15" t="inlineStr">
         <is>
           <t>kept</t>
         </is>
@@ -7076,49 +7100,49 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
     <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="38" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
     <col width="23" customWidth="1" min="24" max="24"/>
     <col width="23" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
-    <col width="37" customWidth="1" min="28" max="28"/>
-    <col width="38" customWidth="1" min="29" max="29"/>
-    <col width="30" customWidth="1" min="30" max="30"/>
-    <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="38" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="34" customWidth="1" min="30" max="30"/>
+    <col width="48" customWidth="1" min="31" max="31"/>
+    <col width="48" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="16" customWidth="1" min="34" max="34"/>
     <col width="19" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
-    <col width="45" customWidth="1" min="37" max="37"/>
-    <col width="38" customWidth="1" min="38" max="38"/>
-    <col width="38" customWidth="1" min="39" max="39"/>
+    <col width="48" customWidth="1" min="37" max="37"/>
+    <col width="48" customWidth="1" min="38" max="38"/>
+    <col width="48" customWidth="1" min="39" max="39"/>
     <col width="15" customWidth="1" min="40" max="40"/>
     <col hidden="1" width="18" customWidth="1" min="41" max="41"/>
     <col hidden="1" width="24" customWidth="1" min="42" max="42"/>
     <col hidden="1" width="24" customWidth="1" min="43" max="43"/>
-    <col hidden="1" width="32" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="26" customWidth="1" min="44" max="44"/>
     <col hidden="1" width="17" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -7345,7 +7369,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="7" t="n">
         <v>2</v>
       </c>
@@ -7534,145 +7558,145 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="n">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>$1,000–$1,500</t>
         </is>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="16" t="n">
         <v>1303</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="16" t="n">
         <v>193</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="16" t="n">
         <v>1303</v>
       </c>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>96203-62-03-50220</t>
         </is>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>18911 S 29 AV W</t>
         </is>
       </c>
-      <c r="J3" s="15" t="n">
+      <c r="J3" s="17" t="n">
         <v>1064.76</v>
       </c>
       <c r="K3" s="10" t="n">
         <v>4000</v>
       </c>
-      <c r="L3" s="15" t="n">
+      <c r="L3" s="17" t="n">
         <v>2935.24</v>
       </c>
-      <c r="M3" s="14" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="N3" s="14" t="inlineStr">
-        <is>
-          <t>Not Checked</t>
-        </is>
-      </c>
-      <c r="O3" s="14" t="inlineStr">
-        <is>
-          <t>Not Checked</t>
-        </is>
-      </c>
-      <c r="P3" s="14" t="inlineStr">
-        <is>
-          <t>Not Checked</t>
-        </is>
-      </c>
-      <c r="Q3" s="14" t="inlineStr">
+      <c r="N3" s="15" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="O3" s="15" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="P3" s="15" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="Q3" s="15" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="R3" s="14" t="inlineStr"/>
-      <c r="S3" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="T3" s="14" t="inlineStr">
+      <c r="R3" s="15" t="inlineStr"/>
+      <c r="S3" s="15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="T3" s="15" t="inlineStr">
         <is>
           <t>South Tulsa / county-edge property, only broad area-level context available in this pass.</t>
         </is>
       </c>
-      <c r="U3" s="14" t="inlineStr">
+      <c r="U3" s="15" t="inlineStr">
         <is>
           <t>ZIP-Level</t>
         </is>
       </c>
-      <c r="V3" s="14" t="inlineStr">
+      <c r="V3" s="15" t="inlineStr">
         <is>
           <t>City of Tulsa public safety resources</t>
         </is>
       </c>
-      <c r="W3" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="X3" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Y3" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="Z3" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AA3" s="14" t="inlineStr"/>
-      <c r="AB3" s="14" t="inlineStr"/>
-      <c r="AC3" s="14" t="inlineStr">
+      <c r="W3" s="15" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="X3" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Y3" s="15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Z3" s="15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AA3" s="15" t="inlineStr"/>
+      <c r="AB3" s="15" t="inlineStr"/>
+      <c r="AC3" s="15" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="AD3" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="AE3" s="14" t="inlineStr">
+      <c r="AD3" s="15" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="AE3" s="15" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="AF3" s="14" t="inlineStr">
+      <c r="AF3" s="15" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="AG3" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AH3" s="14" t="n">
+      <c r="AG3" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH3" s="15" t="n">
         <v>65</v>
       </c>
       <c r="AI3" s="11" t="inlineStr">
@@ -7680,50 +7704,50 @@
           <t>Watchlist</t>
         </is>
       </c>
-      <c r="AJ3" s="14" t="inlineStr">
+      <c r="AJ3" s="15" t="inlineStr">
         <is>
           <t>Priority 3</t>
         </is>
       </c>
-      <c r="AK3" s="14" t="inlineStr">
+      <c r="AK3" s="15" t="inlineStr">
         <is>
           <t>Parcel 96203-62-03-50220 at 18911 S 29 AV W has opening bid 1064.76, max bid 4000.0, grade C, color Blue, crime risk Unknown, and economic signal Unknown.</t>
         </is>
       </c>
-      <c r="AL3" s="14" t="inlineStr">
+      <c r="AL3" s="15" t="inlineStr">
         <is>
           <t>crime context Unknown, economic signal Unknown</t>
         </is>
       </c>
-      <c r="AM3" s="14" t="inlineStr">
+      <c r="AM3" s="15" t="inlineStr">
         <is>
           <t>Verify title, liens, occupancy, and auction-order assumptions before bidding.</t>
         </is>
       </c>
-      <c r="AN3" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AO3" s="14" t="n">
+      <c r="AN3" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AO3" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="AP3" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="14" t="inlineStr">
+      <c r="AP3" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="15" t="inlineStr">
         <is>
           <t>kept</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>4</v>
       </c>
@@ -7912,7 +7936,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="7" t="n">
         <v>5</v>
       </c>
@@ -8101,7 +8125,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="7" t="n">
         <v>7</v>
       </c>
@@ -8290,7 +8314,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="7" t="n">
         <v>8</v>
       </c>
@@ -8479,7 +8503,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="7" t="n">
         <v>9</v>
       </c>
@@ -8668,7 +8692,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="7" t="n">
         <v>10</v>
       </c>
@@ -8857,7 +8881,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="12" t="n">
         <v>11</v>
       </c>
@@ -8874,13 +8898,13 @@
       <c r="D10" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="13" t="n">
         <v>1241</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="13" t="n">
         <v>182</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="13" t="n">
         <v>1081</v>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -8893,13 +8917,13 @@
           <t>1118 E 50 PL N</t>
         </is>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="14" t="n">
         <v>1317.38</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>12000</v>
       </c>
-      <c r="L10" s="13" t="n">
+      <c r="L10" s="14" t="n">
         <v>10682.62</v>
       </c>
       <c r="M10" s="12" t="inlineStr">
@@ -9046,7 +9070,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="n">
         <v>13</v>
       </c>
@@ -9235,7 +9259,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="7" t="n">
         <v>14</v>
       </c>
@@ -9424,7 +9448,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="7" t="n">
         <v>15</v>
       </c>
@@ -9613,7 +9637,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="12" t="n">
         <v>16</v>
       </c>
@@ -9630,13 +9654,13 @@
       <c r="D14" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="13" t="n">
         <v>971</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="13" t="n">
         <v>144</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="13" t="n">
         <v>971</v>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -9649,13 +9673,13 @@
           <t>6369 N BOULDER AV W</t>
         </is>
       </c>
-      <c r="J14" s="13" t="n">
+      <c r="J14" s="14" t="n">
         <v>1693.83</v>
       </c>
       <c r="K14" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="L14" s="13" t="n">
+      <c r="L14" s="14" t="n">
         <v>13306.17</v>
       </c>
       <c r="M14" s="12" t="inlineStr">
@@ -9802,7 +9826,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="7" t="n">
         <v>17</v>
       </c>
@@ -9991,7 +10015,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="7" t="n">
         <v>18</v>
       </c>
@@ -10180,7 +10204,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="12" t="n">
         <v>19</v>
       </c>
@@ -10197,13 +10221,13 @@
       <c r="D17" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="13" t="n">
         <v>1047</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="13" t="n">
         <v>153</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="13" t="n">
         <v>963</v>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -10216,13 +10240,13 @@
           <t>3930 S 61 AV W</t>
         </is>
       </c>
-      <c r="J17" s="13" t="n">
+      <c r="J17" s="14" t="n">
         <v>1716.68</v>
       </c>
       <c r="K17" s="10" t="n">
         <v>14000</v>
       </c>
-      <c r="L17" s="13" t="n">
+      <c r="L17" s="14" t="n">
         <v>12283.32</v>
       </c>
       <c r="M17" s="12" t="inlineStr">
@@ -10321,7 +10345,7 @@
       <c r="AH17" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="AI17" s="7" t="inlineStr">
+      <c r="AI17" s="18" t="inlineStr">
         <is>
           <t>Strong Candidate</t>
         </is>
@@ -10369,153 +10393,153 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="n">
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>$1,500–$2,000</t>
         </is>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="15" t="n">
         <v>41</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="16" t="n">
         <v>204</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="16" t="n">
         <v>204</v>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>13850-93-05-10570</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>2621 E ADMIRAL CT N</t>
         </is>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="17" t="n">
         <v>1759.82</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>8000</v>
       </c>
-      <c r="L18" s="15" t="n">
+      <c r="L18" s="17" t="n">
         <v>6240.18</v>
       </c>
-      <c r="M18" s="14" t="inlineStr">
+      <c r="M18" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="N18" s="14" t="inlineStr">
+      <c r="N18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Checked </t>
         </is>
       </c>
-      <c r="O18" s="14" t="inlineStr">
-        <is>
-          <t>Not Checked</t>
-        </is>
-      </c>
-      <c r="P18" s="14" t="inlineStr">
-        <is>
-          <t>Not Checked</t>
-        </is>
-      </c>
-      <c r="Q18" s="14" t="inlineStr">
+      <c r="O18" s="15" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="P18" s="15" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="Q18" s="15" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="R18" s="14" t="inlineStr"/>
-      <c r="S18" s="14" t="inlineStr">
+      <c r="R18" s="15" t="inlineStr"/>
+      <c r="S18" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="T18" s="14" t="inlineStr">
+      <c r="T18" s="15" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="U18" s="14" t="inlineStr">
+      <c r="U18" s="15" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="V18" s="14" t="inlineStr">
+      <c r="V18" s="15" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="W18" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="X18" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Y18" s="14" t="inlineStr">
+      <c r="W18" s="15" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="X18" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Y18" s="15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="Z18" s="14" t="inlineStr">
+      <c r="Z18" s="15" t="inlineStr">
         <is>
           <t>Possible Match</t>
         </is>
       </c>
-      <c r="AA18" s="14" t="inlineStr">
+      <c r="AA18" s="15" t="inlineStr">
         <is>
           <t>Admiral corridor</t>
         </is>
       </c>
-      <c r="AB18" s="14" t="inlineStr">
+      <c r="AB18" s="15" t="inlineStr">
         <is>
           <t>corridor-level reinvestment context</t>
         </is>
       </c>
-      <c r="AC18" s="14" t="inlineStr">
+      <c r="AC18" s="15" t="inlineStr">
         <is>
           <t>City of Tulsa planning and corridor resources</t>
         </is>
       </c>
-      <c r="AD18" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="AE18" s="14" t="inlineStr">
+      <c r="AD18" s="15" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="AE18" s="15" t="inlineStr">
         <is>
           <t>Address appears on or near the Admiral corridor, where corridor-scale planning and reinvestment signals may matter.</t>
         </is>
       </c>
-      <c r="AF18" s="14" t="inlineStr">
+      <c r="AF18" s="15" t="inlineStr">
         <is>
           <t>Street/corridor name overlap supports only a possible corridor match, not a district-level certainty.</t>
         </is>
       </c>
-      <c r="AG18" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AH18" s="14" t="n">
+      <c r="AG18" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AH18" s="15" t="n">
         <v>66</v>
       </c>
       <c r="AI18" s="11" t="inlineStr">
@@ -10523,50 +10547,50 @@
           <t>Watchlist</t>
         </is>
       </c>
-      <c r="AJ18" s="14" t="inlineStr">
+      <c r="AJ18" s="15" t="inlineStr">
         <is>
           <t>Priority 3</t>
         </is>
       </c>
-      <c r="AK18" s="14" t="inlineStr">
+      <c r="AK18" s="15" t="inlineStr">
         <is>
           <t>Parcel 13850-93-05-10570 at 2621 E ADMIRAL CT N has opening bid 1759.82, max bid 8000.0, grade C, color Blue, crime risk Medium, and economic signal Positive.</t>
         </is>
       </c>
-      <c r="AL18" s="14" t="inlineStr">
+      <c r="AL18" s="15" t="inlineStr">
         <is>
           <t>crime context Medium</t>
         </is>
       </c>
-      <c r="AM18" s="14" t="inlineStr">
+      <c r="AM18" s="15" t="inlineStr">
         <is>
           <t>Verify title, liens, occupancy, and auction-order assumptions before bidding.</t>
         </is>
       </c>
-      <c r="AN18" s="14" t="inlineStr">
+      <c r="AN18" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AO18" s="14" t="n">
+      <c r="AO18" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="AP18" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR18" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS18" s="14" t="inlineStr">
+      <c r="AP18" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="15" t="inlineStr">
         <is>
           <t>kept</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="7" t="n">
         <v>21</v>
       </c>
@@ -10755,7 +10779,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="42" customHeight="1">
       <c r="A20" s="7" t="n">
         <v>22</v>
       </c>
@@ -10944,7 +10968,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="42" customHeight="1">
       <c r="A21" s="7" t="n">
         <v>25</v>
       </c>
@@ -11133,7 +11157,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="7" t="n">
         <v>27</v>
       </c>
@@ -11322,7 +11346,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="42" customHeight="1">
       <c r="A23" s="7" t="n">
         <v>28</v>
       </c>
@@ -11511,7 +11535,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="42" customHeight="1">
       <c r="A24" s="12" t="n">
         <v>29</v>
       </c>
@@ -11528,13 +11552,13 @@
       <c r="D24" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="13" t="n">
         <v>337</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G24" s="13" t="n">
         <v>337</v>
       </c>
       <c r="H24" s="12" t="inlineStr">
@@ -11547,13 +11571,13 @@
           <t>1864 N OWASSO AV E</t>
         </is>
       </c>
-      <c r="J24" s="13" t="n">
+      <c r="J24" s="14" t="n">
         <v>3140.35</v>
       </c>
       <c r="K24" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="L24" s="13" t="n">
+      <c r="L24" s="14" t="n">
         <v>11859.65</v>
       </c>
       <c r="M24" s="12" t="inlineStr">
@@ -11700,7 +11724,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="42" customHeight="1">
       <c r="A25" s="7" t="n">
         <v>31</v>
       </c>
@@ -11889,7 +11913,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="42" customHeight="1">
       <c r="A26" s="7" t="n">
         <v>32</v>
       </c>
@@ -12078,7 +12102,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="42" customHeight="1">
       <c r="A27" s="7" t="n">
         <v>33</v>
       </c>
@@ -12267,7 +12291,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="42" customHeight="1">
       <c r="A28" s="7" t="n">
         <v>34</v>
       </c>
@@ -12456,7 +12480,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="42" customHeight="1">
       <c r="A29" s="7" t="n">
         <v>35</v>
       </c>
@@ -12645,7 +12669,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="42" customHeight="1">
       <c r="A30" s="7" t="n">
         <v>36</v>
       </c>
@@ -12834,7 +12858,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="42" customHeight="1">
       <c r="A31" s="12" t="n">
         <v>37</v>
       </c>
@@ -12851,13 +12875,13 @@
       <c r="D31" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="13" t="n">
         <v>1249</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="13" t="n">
         <v>184</v>
       </c>
-      <c r="G31" s="8" t="n">
+      <c r="G31" s="13" t="n">
         <v>1249</v>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -12870,13 +12894,13 @@
           <t>1641 E 56 ST N TULSA</t>
         </is>
       </c>
-      <c r="J31" s="13" t="n">
+      <c r="J31" s="14" t="n">
         <v>3314.33</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="L31" s="13" t="n">
+      <c r="L31" s="14" t="n">
         <v>11685.67</v>
       </c>
       <c r="M31" s="12" t="inlineStr">
@@ -13023,7 +13047,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="42" customHeight="1">
       <c r="A32" s="7" t="n">
         <v>38</v>
       </c>
@@ -13212,7 +13236,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="42" customHeight="1">
       <c r="A33" s="12" t="n">
         <v>40</v>
       </c>
@@ -13229,13 +13253,13 @@
       <c r="D33" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="13" t="n">
         <v>512</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="13" t="n">
         <v>75</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="13" t="n">
         <v>512</v>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -13248,13 +13272,13 @@
           <t>419 E NEWTON PL N</t>
         </is>
       </c>
-      <c r="J33" s="13" t="n">
+      <c r="J33" s="14" t="n">
         <v>3388.99</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="L33" s="13" t="n">
+      <c r="L33" s="14" t="n">
         <v>11611.01</v>
       </c>
       <c r="M33" s="12" t="inlineStr">
@@ -13401,7 +13425,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="42" customHeight="1">
       <c r="A34" s="12" t="n">
         <v>41</v>
       </c>
@@ -13418,13 +13442,13 @@
       <c r="D34" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="E34" s="13" t="n">
         <v>148</v>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F34" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="13" t="n">
         <v>148</v>
       </c>
       <c r="H34" s="12" t="inlineStr">
@@ -13437,13 +13461,13 @@
           <t>3128 N TROOST PL E</t>
         </is>
       </c>
-      <c r="J34" s="13" t="n">
+      <c r="J34" s="14" t="n">
         <v>3389.11</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>17000</v>
       </c>
-      <c r="L34" s="13" t="n">
+      <c r="L34" s="14" t="n">
         <v>13610.89</v>
       </c>
       <c r="M34" s="12" t="inlineStr">
@@ -13610,49 +13634,49 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
     <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="38" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
     <col width="23" customWidth="1" min="24" max="24"/>
     <col width="23" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
-    <col width="31" customWidth="1" min="28" max="28"/>
-    <col width="37" customWidth="1" min="29" max="29"/>
-    <col width="30" customWidth="1" min="30" max="30"/>
-    <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="38" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="34" customWidth="1" min="30" max="30"/>
+    <col width="48" customWidth="1" min="31" max="31"/>
+    <col width="48" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="16" customWidth="1" min="34" max="34"/>
     <col width="19" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
-    <col width="45" customWidth="1" min="37" max="37"/>
-    <col width="38" customWidth="1" min="38" max="38"/>
-    <col width="38" customWidth="1" min="39" max="39"/>
+    <col width="48" customWidth="1" min="37" max="37"/>
+    <col width="48" customWidth="1" min="38" max="38"/>
+    <col width="48" customWidth="1" min="39" max="39"/>
     <col width="15" customWidth="1" min="40" max="40"/>
     <col hidden="1" width="18" customWidth="1" min="41" max="41"/>
     <col hidden="1" width="24" customWidth="1" min="42" max="42"/>
     <col hidden="1" width="24" customWidth="1" min="43" max="43"/>
-    <col hidden="1" width="32" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="26" customWidth="1" min="44" max="44"/>
     <col hidden="1" width="17" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -13879,7 +13903,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="12" t="n">
         <v>19</v>
       </c>
@@ -13896,13 +13920,13 @@
       <c r="D2" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="13" t="n">
         <v>1047</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="13" t="n">
         <v>153</v>
       </c>
-      <c r="G2" s="8" t="n">
+      <c r="G2" s="13" t="n">
         <v>963</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
@@ -13915,13 +13939,13 @@
           <t>3930 S 61 AV W</t>
         </is>
       </c>
-      <c r="J2" s="13" t="n">
+      <c r="J2" s="14" t="n">
         <v>1716.68</v>
       </c>
       <c r="K2" s="10" t="n">
         <v>14000</v>
       </c>
-      <c r="L2" s="13" t="n">
+      <c r="L2" s="14" t="n">
         <v>12283.32</v>
       </c>
       <c r="M2" s="12" t="inlineStr">
@@ -14020,7 +14044,7 @@
       <c r="AH2" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="AI2" s="7" t="inlineStr">
+      <c r="AI2" s="18" t="inlineStr">
         <is>
           <t>Strong Candidate</t>
         </is>
@@ -14088,50 +14112,50 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
     <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="38" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
     <col width="23" customWidth="1" min="24" max="24"/>
     <col width="23" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="36" customWidth="1" min="27" max="27"/>
-    <col width="38" customWidth="1" min="28" max="28"/>
-    <col width="37" customWidth="1" min="29" max="29"/>
-    <col width="30" customWidth="1" min="30" max="30"/>
-    <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="38" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="34" customWidth="1" min="30" max="30"/>
+    <col width="48" customWidth="1" min="31" max="31"/>
+    <col width="48" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="16" customWidth="1" min="34" max="34"/>
     <col width="19" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
-    <col width="45" customWidth="1" min="37" max="37"/>
-    <col width="38" customWidth="1" min="38" max="38"/>
-    <col width="38" customWidth="1" min="39" max="39"/>
+    <col width="48" customWidth="1" min="37" max="37"/>
+    <col width="48" customWidth="1" min="38" max="38"/>
+    <col width="48" customWidth="1" min="39" max="39"/>
     <col width="15" customWidth="1" min="40" max="40"/>
     <col hidden="1" width="18" customWidth="1" min="41" max="41"/>
     <col hidden="1" width="24" customWidth="1" min="42" max="42"/>
     <col hidden="1" width="24" customWidth="1" min="43" max="43"/>
-    <col hidden="1" width="32" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="26" customWidth="1" min="44" max="44"/>
     <col hidden="1" width="17" customWidth="1" min="45" max="45"/>
-    <col width="31" customWidth="1" min="46" max="46"/>
+    <col width="26" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -14363,7 +14387,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="7" t="n">
         <v>42</v>
       </c>
@@ -14553,7 +14577,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="7" t="n">
         <v>12</v>
       </c>
@@ -14739,7 +14763,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>30</v>
       </c>
@@ -14872,7 +14896,7 @@
       <c r="AH4" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="AI4" s="16" t="inlineStr">
+      <c r="AI4" s="19" t="inlineStr">
         <is>
           <t>High Risk</t>
         </is>
@@ -14925,7 +14949,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="7" t="n">
         <v>6</v>
       </c>
@@ -15115,7 +15139,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="7" t="n">
         <v>24</v>
       </c>
@@ -15305,7 +15329,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="7" t="n">
         <v>26</v>
       </c>
@@ -15495,7 +15519,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="7" t="n">
         <v>39</v>
       </c>
@@ -15685,7 +15709,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="7" t="n">
         <v>1</v>
       </c>
@@ -15824,7 +15848,7 @@
       <c r="AH9" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="AI9" s="7" t="inlineStr">
+      <c r="AI9" s="18" t="inlineStr">
         <is>
           <t>Strong Candidate</t>
         </is>
@@ -15877,7 +15901,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="7" t="n">
         <v>23</v>
       </c>
@@ -16016,7 +16040,7 @@
       <c r="AH10" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="AI10" s="7" t="inlineStr">
+      <c r="AI10" s="18" t="inlineStr">
         <is>
           <t>Strong Candidate</t>
         </is>
@@ -16085,16 +16109,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Parcel ID</t>
@@ -16136,1387 +16160,1387 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>01875-03-19-00200</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>2612 N TRENTON AV E</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="G2" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>05850-03-30-04070</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>1844 N TRENTON AV E</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>07675-02-13-01140</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>4018 N GARRISON AV E</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>10450-03-19-50550</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>3128 N TROOST PL E</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>13850-93-05-10570</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>2621 E ADMIRAL CT N</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>17675-02-24-07570</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>750 E 32 PL N</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>23125-02-25-15350</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>1864 N OWASSO AV E</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>23175-03-30-13610</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>2526 N QUAKER AV E</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>24675-03-31-13270</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>1404 N ST LOUIS AV E</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>25375-03-29-05240</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>3215 E XYLER ST N</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>25500-03-29-06060</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>2625 E TECUMSEH ST N</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>26725-02-25-16640</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>515 E UTE ST N</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>29625-02-36-21010</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>419 E NEWTON PL N</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>38675-93-10-06110</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>1321 S DARLINGTON AV E</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>40250-03-31-14910</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>1945 E NEWTON ST N</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>40250-03-31-15190</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>2143 E NEWTON ST N</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>40825-02-13-08310</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>4337 N GARRISON AV E</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>40850-02-12-07900</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>517 E 47 PL N</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>40875-02-13-11530</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>210 E 44 ST N</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>41025-02-01-04710</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>5901 N GARRISON PL E</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>41025-02-01-05430</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>522 E 59 ST N</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>43300-03-29-09940</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>2311 N ATLANTA AV E</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>44200-02-11-03380</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>4627 N BOSTON AV E</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>44200-02-11-04390</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>4696 N BOULDER AV W</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>44200-02-14-06630</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>18 E 44 PL N</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>44250-02-12-15190</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>549 E 54 PL N</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>47175-03-29-18430</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>1903 N FLORENCE PL E</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>53775-02-02-00220</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>6105 N MAIN ST E TULSA</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>53825-02-02-01690</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>6369 N BOULDER AV W</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>56925-92-20-02770</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>3930 S 61 AV W</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>South Tulsa / county-edge property, only broad area-level context available in this pass.</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>ZIP-Level</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa public safety resources</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>90212-02-12-26700</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>1118 E 50 PL N</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>90306-03-06-24020</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>1641 E 56 ST N TULSA</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-level north Tulsa context from public reporting and city investment patterns.</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>Neighborhood-Level</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>North Tulsa public safety context</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>96203-62-03-50220</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>18911 S 29 AV W</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>South Tulsa / county-edge property, only broad area-level context available in this pass.</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>ZIP-Level</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa public safety resources</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17538,19 +17562,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="37" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Parcel ID</t>
@@ -17607,1626 +17631,1626 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>01875-03-19-00200</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>2612 N TRENTON AV E</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr"/>
-      <c r="F2" s="7" t="inlineStr"/>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr"/>
+      <c r="F2" s="20" t="inlineStr"/>
+      <c r="G2" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I2" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>05850-03-30-04070</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>1844 N TRENTON AV E</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr"/>
-      <c r="F3" s="7" t="inlineStr"/>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr"/>
+      <c r="F3" s="20" t="inlineStr"/>
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>07675-02-13-01140</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>4018 N GARRISON AV E</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr"/>
-      <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr"/>
+      <c r="F4" s="20" t="inlineStr"/>
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>10450-03-19-50550</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>3128 N TROOST PL E</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr"/>
-      <c r="F5" s="12" t="inlineStr"/>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>13850-93-05-10570</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>2621 E ADMIRAL CT N</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Possible Match</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Admiral corridor</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>corridor-level reinvestment context</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa planning and corridor resources</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>Address appears on or near the Admiral corridor, where corridor-scale planning and reinvestment signals may matter.</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>Street/corridor name overlap supports only a possible corridor match, not a district-level certainty.</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>17675-02-24-07570</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>750 E 32 PL N</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>23125-02-25-15350</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>1864 N OWASSO AV E</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr"/>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>23175-03-30-13610</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>2526 N QUAKER AV E</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>24675-03-31-13270</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>1404 N ST LOUIS AV E</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>25375-03-29-05240</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>3215 E XYLER ST N</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>25500-03-29-06060</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>2625 E TECUMSEH ST N</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>26725-02-25-16640</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>515 E UTE ST N</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>29625-02-36-21010</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>419 E NEWTON PL N</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr"/>
-      <c r="F14" s="12" t="inlineStr"/>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K14" s="12" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>38675-93-10-06110</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>1321 S DARLINGTON AV E</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>40250-03-31-14910</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>1945 E NEWTON ST N</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr"/>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>40250-03-31-15190</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>2143 E NEWTON ST N</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr"/>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr"/>
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>40825-02-13-08310</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>4337 N GARRISON AV E</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>40850-02-12-07900</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>517 E 47 PL N</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr"/>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>40875-02-13-11530</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>210 E 44 ST N</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr"/>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr"/>
+      <c r="F20" s="20" t="inlineStr"/>
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>41025-02-01-04710</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>5901 N GARRISON PL E</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr"/>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>41025-02-01-05430</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>522 E 59 ST N</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr"/>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>43300-03-29-09940</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>2311 N ATLANTA AV E</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr"/>
+      <c r="F23" s="20" t="inlineStr"/>
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>44200-02-11-03380</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>4627 N BOSTON AV E</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr"/>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>44200-02-11-04390</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>4696 N BOULDER AV W</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>44200-02-14-06630</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>18 E 44 PL N</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr"/>
+      <c r="F26" s="20" t="inlineStr"/>
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr">
+      <c r="K26" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>44250-02-12-15190</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>549 E 54 PL N</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr"/>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>47175-03-29-18430</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>1903 N FLORENCE PL E</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr"/>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr"/>
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr">
+      <c r="K28" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>53775-02-02-00220</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>6105 N MAIN ST E TULSA</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr"/>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr"/>
+      <c r="F29" s="20" t="inlineStr"/>
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="K29" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>53825-02-02-01690</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>6369 N BOULDER AV W</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr"/>
-      <c r="F30" s="12" t="inlineStr"/>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr"/>
+      <c r="F30" s="20" t="inlineStr"/>
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I30" s="12" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J30" s="12" t="inlineStr">
+      <c r="J30" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K30" s="12" t="inlineStr">
+      <c r="K30" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>56925-92-20-02770</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>3930 S 61 AV W</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr"/>
-      <c r="F31" s="12" t="inlineStr"/>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr"/>
+      <c r="F31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="J31" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr">
+      <c r="K31" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>90212-02-12-26700</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>1118 E 50 PL N</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="inlineStr"/>
-      <c r="F32" s="12" t="inlineStr"/>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr"/>
+      <c r="F32" s="20" t="inlineStr"/>
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J32" s="12" t="inlineStr">
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K32" s="12" t="inlineStr">
+      <c r="K32" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>90306-03-06-24020</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>1641 E 56 ST N TULSA</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr"/>
-      <c r="F33" s="12" t="inlineStr"/>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr"/>
+      <c r="F33" s="20" t="inlineStr"/>
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J33" s="12" t="inlineStr">
+      <c r="J33" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K33" s="12" t="inlineStr">
+      <c r="K33" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>96203-62-03-50220</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>18911 S 29 AV W</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr"/>
-      <c r="F34" s="14" t="inlineStr"/>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr"/>
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>City of Tulsa development resources</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cityoftulsa.org/</t>
-        </is>
-      </c>
-      <c r="I34" s="14" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cityoftulsa.org/</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>No credible project or district match was established from the available row data in this batch.</t>
         </is>
       </c>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
         <is>
           <t>Avoided generic city-level matching without clearer location evidence.</t>
         </is>
       </c>
-      <c r="K34" s="14" t="inlineStr">
+      <c r="K34" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19247,11 +19271,11 @@
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
@@ -19263,163 +19287,163 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>previous active property count</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="21" t="n">
         <v>42</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>deleted property count</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="21" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>final active property count</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="21" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Color: Green</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="21" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Color: Purple</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="21" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Color: Blue</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="21" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Grade: C</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="21" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Grade: B</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="21" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Grade: A</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="21" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>ai_final_category: Watchlist</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="21" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>ai_final_category: Strong Candidate</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>ai_bid_priority: Priority 3</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="21" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>ai_bid_priority: Priority 2</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>total opening bid</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="21" t="n">
         <v>73216</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>total max bid</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="21" t="n">
         <v>338500</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>number of properties with blank max bid</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="21" t="n">
         <v>0</v>
       </c>
     </row>
